--- a/data/trans_dic/P02E$ssociales-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,54</t>
+          <t>2,2; 8,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,82</t>
+          <t>1,56; 9,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,54; 5,08</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,17</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 5,28</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,54</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,05</t>
+          <t>0,23; 2,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,21</t>
+          <t>2,19; 5,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,98</t>
+          <t>0,7; 3,93</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,36</t>
+          <t>0,46; 2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,17</t>
+          <t>0,41; 2,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,55</t>
+          <t>0,33; 1,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,49</t>
+          <t>0,65; 2,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,44</t>
+          <t>0,51; 1,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,0</t>
+          <t>0,72; 2,13</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,67</t>
+          <t>0,95; 2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,43</t>
+          <t>0,71; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,07</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,96</t>
+          <t>0,81; 2,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,73</t>
+          <t>0,49; 1,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,84</t>
+          <t>0,18; 0,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,93</t>
+          <t>1,03; 1,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,74</t>
+          <t>0,71; 1,72</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5023</t>
+          <t>0; 4866</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3997; 15466</t>
+          <t>3976; 15727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2130; 11256</t>
+          <t>1984; 11679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5879</t>
+          <t>0; 6790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6145; 20485</t>
+          <t>5963; 19716</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7012</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>893; 7873</t>
+          <t>894; 7772</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12269; 29649</t>
+          <t>12443; 30498</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2765; 12938</t>
+          <t>2277; 12776</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 4598</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2990; 14740</t>
+          <t>2856; 13447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1941; 10422</t>
+          <t>1949; 10631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6393</t>
+          <t>0; 6820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3007; 14002</t>
+          <t>3000; 14163</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4931; 17337</t>
+          <t>4567; 16934</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>881; 7430</t>
+          <t>880; 8630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7941; 21957</t>
+          <t>7833; 23965</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8706; 23581</t>
+          <t>8524; 25070</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1936</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8527</t>
+          <t>0; 6519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5111</t>
+          <t>0; 5089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5721</t>
+          <t>0; 5136</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6274</t>
+          <t>0; 5508</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7178</t>
+          <t>0; 8280</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2034</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 6502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9875; 26290</t>
+          <t>9376; 25877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5145; 18290</t>
+          <t>5316; 19574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1878; 10719</t>
+          <t>1050; 10784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12289; 29755</t>
+          <t>12338; 30853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5423; 19232</t>
+          <t>5455; 18498</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2909; 13638</t>
+          <t>2875; 13372</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24778; 48170</t>
+          <t>25663; 48320</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13168; 32317</t>
+          <t>13223; 31955</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,69</t>
+          <t>2,22; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,16</t>
+          <t>1,52; 9,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,08</t>
+          <t>1,62; 5,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,02</t>
+          <t>0,23; 2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,36</t>
+          <t>2,14; 5,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,93</t>
+          <t>0,69; 3,93</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,15</t>
+          <t>0,47; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,21</t>
+          <t>0,41; 2,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,57</t>
+          <t>0,33; 1,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,43</t>
+          <t>0,65; 2,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,57</t>
+          <t>0,51; 1,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,13</t>
+          <t>0,69; 2,01</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,63</t>
+          <t>0,96; 2,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,6</t>
+          <t>0,7; 2,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,03</t>
+          <t>0,79; 1,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,67</t>
+          <t>0,47; 1,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,82</t>
+          <t>0,17; 0,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,93</t>
+          <t>1,02; 1,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,72</t>
+          <t>0,71; 1,73</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4866</t>
+          <t>0; 5237</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3976; 15727</t>
+          <t>4023; 14833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1984; 11679</t>
+          <t>1935; 12119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6790</t>
+          <t>0; 6552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5963; 19716</t>
+          <t>6292; 20238</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 5453</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>894; 7772</t>
+          <t>890; 7673</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12443; 30498</t>
+          <t>12179; 30148</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2277; 12776</t>
+          <t>2231; 12780</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4598</t>
+          <t>0; 4534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2856; 13447</t>
+          <t>2931; 14673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1949; 10631</t>
+          <t>1980; 11611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6820</t>
+          <t>0; 5929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3000; 14163</t>
+          <t>2986; 13916</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4567; 16934</t>
+          <t>4562; 17693</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>880; 8630</t>
+          <t>872; 7496</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7833; 23965</t>
+          <t>7789; 21966</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8524; 25070</t>
+          <t>8139; 23697</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6519</t>
+          <t>0; 4692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5089</t>
+          <t>0; 5171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5136</t>
+          <t>0; 5048</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5508</t>
+          <t>0; 5618</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 8280</t>
+          <t>0; 7684</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6502</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9376; 25877</t>
+          <t>9443; 25210</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5316; 19574</t>
+          <t>5243; 17997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1050; 10784</t>
+          <t>1897; 11091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12338; 30853</t>
+          <t>12014; 29190</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5455; 18498</t>
+          <t>5211; 19009</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2875; 13372</t>
+          <t>2810; 13528</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25663; 48320</t>
+          <t>25432; 48525</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13223; 31955</t>
+          <t>13275; 32237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
